--- a/Server/Application/ReportGeneration/report_template.xlsx
+++ b/Server/Application/ReportGeneration/report_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\helix\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\LTPulse\Server\Application\ReportGeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -98,7 +98,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Количество обращений в состоянии "В работе"</a:t>
+              <a:t>Количество не закрытых инцидентов с разбивкой по времени в работе</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -116,18 +116,20 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:areaChart>
+        <c:grouping val="percentStacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Всего в работе</c:v>
+            <c:v>0-8</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C3D69B"/>
+            </a:solidFill>
+          </c:spPr>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -136,20 +138,17 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:layout/>
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -165,12 +164,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -178,12 +176,12 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9D8B-45B7-9087-3E4AB723CB5C}"/>
+              <c16:uniqueId val="{00000000-AC07-46DA-8A29-C29DF671ED0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -191,11 +189,13 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Кол-во баллов за месяц</c:v>
+            <c:v>8-16</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFF2CC"/>
+            </a:solidFill>
+          </c:spPr>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -204,20 +204,17 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:layout/>
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -233,12 +230,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -246,12 +242,12 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9D8B-45B7-9087-3E4AB723CB5C}"/>
+              <c16:uniqueId val="{00000001-AC07-46DA-8A29-C29DF671ED0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -259,11 +255,13 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>Июль 2025</c:v>
+            <c:v>16-24</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+          </c:spPr>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -272,20 +270,17 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:layout/>
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -301,12 +296,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -314,12 +308,12 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9D8B-45B7-9087-3E4AB723CB5C}"/>
+              <c16:uniqueId val="{00000002-AC07-46DA-8A29-C29DF671ED0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -327,11 +321,13 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>Август 2025</c:v>
+            <c:v>&gt;24</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF4F4F"/>
+            </a:solidFill>
+          </c:spPr>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -340,20 +336,17 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:layout/>
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -369,12 +362,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -382,231 +374,26 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-9D8B-45B7-9087-3E4AB723CB5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>Сентябрь 2025</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-9D8B-45B7-9087-3E4AB723CB5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>Октябрь 2025</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-9D8B-45B7-9087-3E4AB723CB5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:v>Ноябрь 2025</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-9D8B-45B7-9087-3E4AB723CB5C}"/>
+              <c16:uniqueId val="{00000003-AC07-46DA-8A29-C29DF671ED0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-      </c:lineChart>
+      </c:areaChart>
       <c:catAx>
         <c:axId val="1"/>
         <c:scaling>
@@ -639,11 +426,12 @@
         <c:axId val="2"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.60000000000000009"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
@@ -690,143 +478,6 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="1"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1080" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Поступило обращений всего</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -921,7 +572,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -929,7 +580,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -1054,408 +705,6 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Количество не закрытых инцидентов с разбивкой по времени в работе</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:areaChart>
-        <c:grouping val="percentStacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>0-8</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="C3D69B"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AC07-46DA-8A29-C29DF671ED0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>8-16</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFF2CC"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AC07-46DA-8A29-C29DF671ED0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>16-24</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AC07-46DA-8A29-C29DF671ED0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>&gt;24</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF4F4F"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-AC07-46DA-8A29-C29DF671ED0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:areaChart>
-      <c:catAx>
-        <c:axId val="1"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0.60000000000000009"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1080" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Snowball</a:t>
             </a:r>
@@ -1529,7 +778,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -1537,7 +786,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -1597,7 +846,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -1605,12 +854,218 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-506C-4757-9045-65E2000E4C84}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" kern="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" kern="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1080" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Общее количество не закрытых обращений</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Хвост</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator>
+</c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0B41-4B2E-8206-DE9D4C4495D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1731,7 +1186,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Общее количество не закрытых обращений</a:t>
+              <a:t>Количество не закрытых обращений старше 4 недель</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1756,7 +1211,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Хвост</c:v>
+            <c:v>Старше 4 недель</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
@@ -1803,7 +1258,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -1811,12 +1266,12 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B41-4B2E-8206-DE9D4C4495D7}"/>
+              <c16:uniqueId val="{00000000-754C-48FE-B9A3-434F7E087004}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1937,7 +1392,15 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Количество не закрытых обращений старше 4 недель</a:t>
+              <a:t>Количество не закрытых инцидентов с разбивкой по времени в работе </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>c </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>с учётом приоритета</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1955,18 +1418,23 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:areaChart>
+        <c:grouping val="percentStacked"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="3"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Старше 4 недель</c:v>
+            <c:v>&lt;0.25</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C3D69B"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1975,54 +1443,182 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>
-</c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:layout/>
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>#REF!</c:f>
+              <c:f>Графики!$AA$165:$AD$165</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredCategoryTitle>
-                <c15:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                  </c:strRef>
-                </c15:cat>
-              </c15:filteredCategoryTitle>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-754C-48FE-B9A3-434F7E087004}"/>
+              <c16:uniqueId val="{00000009-1F0C-4057-AEB0-99894C53FDCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>0.25-0.5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFF2CC"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$AA$166:$AD$166</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-1F0C-4057-AEB0-99894C53FDCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>0.5-0.75</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$AA$167:$AD$167</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-1F0C-4057-AEB0-99894C53FDCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>&gt;0.75</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF4F4F"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$AA$168:$AD$168</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1F0C-4057-AEB0-99894C53FDCC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2034,10 +1630,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-      </c:lineChart>
+      </c:areaChart>
       <c:catAx>
         <c:axId val="1"/>
         <c:scaling>
@@ -2070,150 +1665,7 @@
         <c:axId val="2"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="1"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1080" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Количество не закрытых инцидентов с разбивкой по времени в работе </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>c </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>с учётом приоритета</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:areaChart>
-        <c:grouping val="percentStacked"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:areaChart>
-      <c:catAx>
-        <c:axId val="1"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="cross"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" kern="1200"/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:min val="0.60000000000000009"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2264,7 +1716,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2355,7 +1807,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2363,7 +1815,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -2467,9 +1919,9 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="1"/>
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
@@ -2512,6 +1964,28 @@
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Внешние сообщения</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-88FD-4D6A-9A90-7C82139FE8A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -2559,6 +2033,7 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
@@ -2604,7 +2079,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2699,7 +2174,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2707,7 +2182,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -2767,7 +2242,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2775,7 +2250,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -2835,7 +2310,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2843,7 +2318,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -2903,7 +2378,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:strRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2911,7 +2386,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:strRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -3014,38 +2489,168 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1080" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Поступило обращений всего</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Поступило всего</c:v>
+          </c:tx>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3C46-4360-9586-B7A57949A6EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" kern="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" kern="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Количество обращений в состоянии &quot;В работе&quot;"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3070,7 +2675,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3100,7 +2705,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3130,7 +2735,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3160,7 +2765,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3190,7 +2795,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3220,7 +2825,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3250,7 +2855,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3280,7 +2885,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3310,7 +2915,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3340,7 +2945,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
